--- a/metadata/plate_metadata/20260324_cep290_18hpf_plate01_well_metadata.xlsx
+++ b/metadata/plate_metadata/20260324_cep290_18hpf_plate01_well_metadata.xlsx
@@ -2039,7 +2039,7 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="K2" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -2183,17 +2183,17 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
@@ -2208,17 +2208,17 @@
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2240,12 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
     </row>
